--- a/artfynd/A 1279-2024 artfynd.xlsx
+++ b/artfynd/A 1279-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1279-2024 artfynd.xlsx
+++ b/artfynd/A 1279-2024 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>117827552</v>
       </c>
       <c r="B4" t="n">
-        <v>56985</v>
+        <v>56986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1279-2024 artfynd.xlsx
+++ b/artfynd/A 1279-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,6 +1054,135 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123391055</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57428</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Edssved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>499622</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6968457</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Norr om vägen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Hedenbo</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Hedenbo</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1279-2024 artfynd.xlsx
+++ b/artfynd/A 1279-2024 artfynd.xlsx
@@ -1059,7 +1059,7 @@
         <v>123391055</v>
       </c>
       <c r="B5" t="n">
-        <v>57428</v>
+        <v>57431</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1279-2024 artfynd.xlsx
+++ b/artfynd/A 1279-2024 artfynd.xlsx
@@ -1059,7 +1059,7 @@
         <v>123391055</v>
       </c>
       <c r="B5" t="n">
-        <v>57431</v>
+        <v>57437</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1279-2024 artfynd.xlsx
+++ b/artfynd/A 1279-2024 artfynd.xlsx
@@ -1059,7 +1059,7 @@
         <v>123391055</v>
       </c>
       <c r="B5" t="n">
-        <v>57437</v>
+        <v>57440</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1279-2024 artfynd.xlsx
+++ b/artfynd/A 1279-2024 artfynd.xlsx
@@ -1059,7 +1059,7 @@
         <v>123391055</v>
       </c>
       <c r="B5" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 1279-2024 artfynd.xlsx
+++ b/artfynd/A 1279-2024 artfynd.xlsx
@@ -1059,12 +1059,7 @@
         <v>123391055</v>
       </c>
       <c r="B5" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1279-2024 artfynd.xlsx
+++ b/artfynd/A 1279-2024 artfynd.xlsx
@@ -1059,7 +1059,7 @@
         <v>123391055</v>
       </c>
       <c r="B5" t="n">
-        <v>57493</v>
+        <v>57494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1279-2024 artfynd.xlsx
+++ b/artfynd/A 1279-2024 artfynd.xlsx
@@ -1059,7 +1059,7 @@
         <v>123391055</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1279-2024 artfynd.xlsx
+++ b/artfynd/A 1279-2024 artfynd.xlsx
@@ -1059,7 +1059,7 @@
         <v>123391055</v>
       </c>
       <c r="B5" t="n">
-        <v>57498</v>
+        <v>57499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
